--- a/results/naturverbundenheit/base_data/nature-dataset_explainable_dataset_scaled.xlsx
+++ b/results/naturverbundenheit/base_data/nature-dataset_explainable_dataset_scaled.xlsx
@@ -522,52 +522,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6176679786290794</v>
+        <v>0.6167458703840271</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08207171468240484</v>
+        <v>0.08204645537733803</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02736105556555178</v>
+        <v>0.02959897587113682</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7167803888282427</v>
+        <v>0.7178430083755331</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9508004083873446</v>
+        <v>0.950287166695625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9284054678823246</v>
+        <v>0.9287143150966545</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03434963473596904</v>
+        <v>0.03670536502276257</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8613846342961664</v>
+        <v>0.8599524655133373</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9893528197084028</v>
+        <v>0.988549754106096</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8922409301230888</v>
+        <v>0.8910467902613531</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7736472582902336</v>
+        <v>0.7724356424494736</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8857840282495526</v>
+        <v>0.8851256975313536</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5512259414459237</v>
+        <v>0.5512126118288451</v>
       </c>
       <c r="O2" t="n">
-        <v>0.254010676859394</v>
+        <v>0.2532649905354909</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5782589870553847</v>
+        <v>0.5780399064549343</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9098644163931713</v>
+        <v>0.9106499655747434</v>
       </c>
     </row>
     <row r="3">
@@ -577,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2620161189727044</v>
+        <v>0.2621558334685638</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1451038832128032</v>
+        <v>0.1446598589812312</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03945483488208082</v>
+        <v>0.0376235622152789</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6908409525866224</v>
+        <v>0.6881106595148975</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4679777641628109</v>
+        <v>0.4674275687056423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4941798361147324</v>
+        <v>0.495308761208283</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4446657554459906</v>
+        <v>0.4429441423144691</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8700192474075658</v>
+        <v>0.8688962141816033</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8014718305740297</v>
+        <v>0.8004082642737339</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6758259172803401</v>
+        <v>0.6740871942465697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5593232409200702</v>
+        <v>0.5591532435991566</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8533538929522925</v>
+        <v>0.855491387017442</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3218402276243342</v>
+        <v>0.3223226923142776</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8657649323515764</v>
+        <v>0.8661674501602533</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3511345040469886</v>
+        <v>0.3511177386200265</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.7248220215255892</v>
+        <v>0.7266144233657066</v>
       </c>
     </row>
     <row r="4">
@@ -632,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3719468037621125</v>
+        <v>0.3738403242277377</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08664987372014371</v>
+        <v>0.08464676634691695</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0471659011514438</v>
+        <v>0.04682306810619698</v>
       </c>
       <c r="E4" t="n">
-        <v>1.000704565481428</v>
+        <v>0.999246582010471</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9182352181380953</v>
+        <v>0.9171859305153507</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9240988195615348</v>
+        <v>0.9223348579305538</v>
       </c>
       <c r="H4" t="n">
-        <v>0.386433375550214</v>
+        <v>0.3859043577955559</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8213357147168885</v>
+        <v>0.820264694083471</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9756400135348241</v>
+        <v>0.972453153457145</v>
       </c>
       <c r="K4" t="n">
-        <v>1.000565696395616</v>
+        <v>0.9999993193579596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6427758067106716</v>
+        <v>0.6438915845986628</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9128564804525205</v>
+        <v>0.9139822617592652</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1204995524446102</v>
+        <v>0.1201036450047527</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5612676793214327</v>
+        <v>0.5627128543839063</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08060209180900468</v>
+        <v>0.08136439927301888</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9407465190128113</v>
+        <v>0.940879716820744</v>
       </c>
     </row>
     <row r="5">
@@ -687,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4169804343025913</v>
+        <v>0.4182433536742426</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5789673199939666</v>
+        <v>0.577298400951282</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9999658558323683</v>
+        <v>0.999782434360652</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5558708313110104</v>
+        <v>0.5581947578437982</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2140053931050627</v>
+        <v>0.2170312722764489</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3540035688002096</v>
+        <v>0.3543098704576793</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06314690955892568</v>
+        <v>0.06374890106099868</v>
       </c>
       <c r="I5" t="n">
-        <v>0.629933107567664</v>
+        <v>0.6304301155389691</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7973636283594228</v>
+        <v>0.7964021512899606</v>
       </c>
       <c r="K5" t="n">
-        <v>0.703950180385483</v>
+        <v>0.7048209356023521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3650353174576971</v>
+        <v>0.3636482315858835</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8495927954900582</v>
+        <v>0.8494424194086266</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07491294773024396</v>
+        <v>0.07789708691851055</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3376865733246179</v>
+        <v>0.3395294995904122</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6946761109572828</v>
+        <v>0.6943145491332132</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7222420686860525</v>
+        <v>0.7219944036373477</v>
       </c>
     </row>
     <row r="6">
@@ -742,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1539357537847924</v>
+        <v>0.153484998354563</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2644219604565707</v>
+        <v>0.2640730538735137</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006322181204355201</v>
+        <v>0.006445032915717751</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7085831866944906</v>
+        <v>0.709854678306526</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4571519596513561</v>
+        <v>0.4571695002432836</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5397023226800327</v>
+        <v>0.5417676942483862</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03873380023294636</v>
+        <v>0.04053805835169234</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8206309400890029</v>
+        <v>0.819039141050134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8031862795187815</v>
+        <v>0.803230696357443</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6564623354636354</v>
+        <v>0.6579139646189474</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5461274494491614</v>
+        <v>0.5465252813146017</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8237447880407983</v>
+        <v>0.8241839880539231</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2347736515726184</v>
+        <v>0.2353038376689024</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7765304582810905</v>
+        <v>0.7765170715283308</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5510428901839088</v>
+        <v>0.5527236640165756</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.7138734681136837</v>
+        <v>0.7135652710861466</v>
       </c>
     </row>
     <row r="7">
@@ -797,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1438920918929652</v>
+        <v>0.1484385768062479</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2036593848539389</v>
+        <v>0.2040085709406203</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0003258764585360135</v>
+        <v>0.0008045310158226003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5257265233966725</v>
+        <v>0.5258345850440982</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5339030006515396</v>
+        <v>0.5372624331124387</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5954812006998975</v>
+        <v>0.5947194376470961</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0005176622066152245</v>
+        <v>0.0005501709399067527</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8096813870502688</v>
+        <v>0.8104867995034469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8486848354151372</v>
+        <v>0.8482219514175049</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7762737234264743</v>
+        <v>0.7768068381981115</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5951648861468544</v>
+        <v>0.594906416351115</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8672224266104426</v>
+        <v>0.8671398585415406</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04917701481733884</v>
+        <v>0.04891103051413957</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8651143683713133</v>
+        <v>0.8637795403509024</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4270760125554276</v>
+        <v>0.4264696230158487</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8046576056554666</v>
+        <v>0.8059839970937909</v>
       </c>
     </row>
     <row r="8">
@@ -852,107 +852,107 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1068972288999689</v>
+        <v>0.1071791018177677</v>
       </c>
       <c r="C8" t="n">
-        <v>0.216194883367397</v>
+        <v>0.2169787789302119</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002226978867277917</v>
+        <v>0.003771719199727706</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4920396740127096</v>
+        <v>0.4877550537480624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3495886840437859</v>
+        <v>0.3498217429400812</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3546435127104866</v>
+        <v>0.3563062225944057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0006876098471936241</v>
+        <v>0.003301173288572829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8312990252267068</v>
+        <v>0.8309417358126999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7913431889087271</v>
+        <v>0.7913371001589173</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6644458254546679</v>
+        <v>0.6642446013497884</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5438226314998893</v>
+        <v>0.5442259276191698</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8299103656406949</v>
+        <v>0.8314824884100527</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1299670974679699</v>
+        <v>0.1302347357019062</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6456679299318526</v>
+        <v>0.6455974399552563</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6218407765152022</v>
+        <v>0.6229488053314906</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.7283942885765601</v>
+        <v>0.7276001719694358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ecuador </t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1877452509067191</v>
+        <v>0.1861366483934974</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2404530546663088</v>
+        <v>0.2416614058225823</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002884046497229446</v>
+        <v>0.002652123013361601</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6300211063702708</v>
+        <v>0.6318034723919183</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4613014315690584</v>
+        <v>0.459581620083345</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5032102903894216</v>
+        <v>0.5040717862539211</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003318438990034576</v>
+        <v>0.004173835848974128</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6405213683032202</v>
+        <v>0.6396652345412595</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7950259943596678</v>
+        <v>0.7945634109137635</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6430082314682398</v>
+        <v>0.6437744637405588</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5983653121877245</v>
+        <v>0.5981160155324429</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8418949253591</v>
+        <v>0.8396006927622173</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07688948190522667</v>
+        <v>0.07576559522990782</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7322417722210149</v>
+        <v>0.7310902395810822</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2685360150161957</v>
+        <v>0.2706409581618831</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6620245012454691</v>
+        <v>0.6612562008841775</v>
       </c>
     </row>
     <row r="10">
@@ -962,107 +962,107 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3949973483410297</v>
+        <v>0.3948177030110865</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1329409129614802</v>
+        <v>0.1320493373858222</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02433084465494949</v>
+        <v>0.02246109543945101</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4656458863563647</v>
+        <v>0.4663574536490365</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8541851191789129</v>
+        <v>0.8552990035593148</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8991967354917525</v>
+        <v>0.9003263433283453</v>
       </c>
       <c r="H10" t="n">
-        <v>8.826122594947334e-05</v>
+        <v>0.001132945782378333</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8113893153189877</v>
+        <v>0.8104779575068891</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9439479171482723</v>
+        <v>0.9426533165223285</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8648861803712382</v>
+        <v>0.8641675371589508</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8047025845092869</v>
+        <v>0.803499000219419</v>
       </c>
       <c r="M10" t="n">
-        <v>0.952998192136791</v>
+        <v>0.9532632521682015</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0008606526680295273</v>
+        <v>-0.0002913819853926463</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4589136397990148</v>
+        <v>0.4599373101476384</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6465591472315428</v>
+        <v>0.6465271742558578</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.979436837310637</v>
+        <v>0.9790615600471388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Germany </t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2835143818866702</v>
+        <v>0.2819375339363474</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1443161830217413</v>
+        <v>0.1451730722795953</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05340241949701218</v>
+        <v>0.05255912514826606</v>
       </c>
       <c r="E11" t="n">
-        <v>0.461092320615633</v>
+        <v>0.4584661975844332</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7836664841786544</v>
+        <v>0.7817538337593775</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8810403403425745</v>
+        <v>0.88128663095184</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03219456607665996</v>
+        <v>0.03081684225947579</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7818633554465372</v>
+        <v>0.7805318544399114</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9909978534225383</v>
+        <v>0.9921819279353681</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9121202490910546</v>
+        <v>0.912181139420722</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8029406736709269</v>
+        <v>0.8040896507992352</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9639971795420592</v>
+        <v>0.9631162169419233</v>
       </c>
       <c r="N11" t="n">
-        <v>0.005403153486558733</v>
+        <v>0.006484515150075858</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4743724005366669</v>
+        <v>0.4768837569107178</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5898667661540214</v>
+        <v>0.5888859900969011</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.9930380615098362</v>
+        <v>0.9920793387635671</v>
       </c>
     </row>
     <row r="12">
@@ -1072,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.3595168191346035</v>
+        <v>0.3575240532895152</v>
       </c>
       <c r="C12" t="n">
-        <v>1.00094334116053</v>
+        <v>1.002178128609494</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2128576544049365</v>
+        <v>0.2104158784786175</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3870470731060517</v>
+        <v>0.3887815342054518</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08072286571786806</v>
+        <v>0.08215841996439842</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1330890120688334</v>
+        <v>0.133293261972358</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0180649993693013</v>
+        <v>0.02035253822775249</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3498250194587444</v>
+        <v>0.3496830874887826</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6745072040985168</v>
+        <v>0.6756037643981649</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6066722981794451</v>
+        <v>0.6062329451725862</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2444396566373597</v>
+        <v>0.2428407300788131</v>
       </c>
       <c r="M12" t="n">
-        <v>0.708841299611134</v>
+        <v>0.7073465221753987</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1026788716471711</v>
+        <v>0.1023643115413793</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3546001461200326</v>
+        <v>0.3529059062229479</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7469626982331077</v>
+        <v>0.7483225279012742</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.7002549053343975</v>
+        <v>0.696796084162363</v>
       </c>
     </row>
     <row r="13">
@@ -1127,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1744560774102852</v>
+        <v>0.1737417932568662</v>
       </c>
       <c r="C13" t="n">
-        <v>0.09759488816083145</v>
+        <v>0.09514717316448791</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002711040676554817</v>
+        <v>0.003763938369999125</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5134152337066252</v>
+        <v>0.511900362615458</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9983940624971528</v>
+        <v>0.999090292822353</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9489856340343356</v>
+        <v>0.9498629301285655</v>
       </c>
       <c r="H13" t="n">
-        <v>0.001981105762180068</v>
+        <v>0.001630355705023394</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6399045664673468</v>
+        <v>0.6403567344259663</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9993615647234511</v>
+        <v>1.001511521054187</v>
       </c>
       <c r="K13" t="n">
-        <v>0.901057974751712</v>
+        <v>0.9004834092864062</v>
       </c>
       <c r="L13" t="n">
-        <v>0.73903501503878</v>
+        <v>0.7391255024526968</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9471853677341858</v>
+        <v>0.9460860813085333</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0009523598825737265</v>
+        <v>-9.001880025692013e-06</v>
       </c>
       <c r="O13" t="n">
-        <v>0.008194083830960017</v>
+        <v>0.00575303540556665</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8119054293670168</v>
+        <v>0.8120292198513059</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.9579828988889088</v>
+        <v>0.9585257191643878</v>
       </c>
     </row>
     <row r="14">
@@ -1182,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4093289371013375</v>
+        <v>0.408732769164749</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1582230632860197</v>
+        <v>0.1551939990427779</v>
       </c>
       <c r="D14" t="n">
-        <v>0.08774743279833939</v>
+        <v>0.08627414295416386</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5618130521884456</v>
+        <v>0.5622031527951985</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8201905604329028</v>
+        <v>0.82268094505719</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8862075525606385</v>
+        <v>0.8853510026973147</v>
       </c>
       <c r="H14" t="n">
-        <v>0.003549697652405577</v>
+        <v>0.002489525768340468</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9213717204780241</v>
+        <v>0.9190903792878161</v>
       </c>
       <c r="J14" t="n">
-        <v>0.962838144010056</v>
+        <v>0.961906293140539</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8793220897683131</v>
+        <v>0.8790006691387656</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7357978512041932</v>
+        <v>0.7367856167539932</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9333622899005157</v>
+        <v>0.9330838032276132</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01308145547493457</v>
+        <v>0.01184681346486243</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9950196551113718</v>
+        <v>0.9950083029814912</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1539953432721518</v>
+        <v>0.1501202477903108</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8760672419158017</v>
+        <v>0.8772872504997521</v>
       </c>
     </row>
     <row r="15">
@@ -1237,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1416683116233938</v>
+        <v>0.1409101750577046</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2639415877180148</v>
+        <v>0.2650952076942615</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001532798535918867</v>
+        <v>0.001512222586326006</v>
       </c>
       <c r="E15" t="n">
-        <v>0.47293087001593</v>
+        <v>0.4717674453890581</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3125901937865987</v>
+        <v>0.31260693449027</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2791102968593775</v>
+        <v>0.2815555537769199</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0002168634576904839</v>
+        <v>-0.0008634168906856477</v>
       </c>
       <c r="I15" t="n">
-        <v>0.281625010344138</v>
+        <v>0.2798377061075103</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6284600765295683</v>
+        <v>0.6294142700551053</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5773954717723894</v>
+        <v>0.5795719119409368</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3961592291546516</v>
+        <v>0.3963230816908835</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7161105472772523</v>
+        <v>0.7154653227980182</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06600673115920708</v>
+        <v>0.06465942833276582</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09110739951234505</v>
+        <v>0.08956230749448189</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6003680192254187</v>
+        <v>0.5995280311033021</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6204804640259128</v>
+        <v>0.6195483477373327</v>
       </c>
     </row>
     <row r="16">
@@ -1292,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3077794105596954</v>
+        <v>0.3078045982793385</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2403325214871505</v>
+        <v>0.2402006952755213</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03190043801608356</v>
+        <v>0.03216047057819435</v>
       </c>
       <c r="E16" t="n">
-        <v>0.562366595644535</v>
+        <v>0.5617629061019233</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3575389716410958</v>
+        <v>0.3548466433440839</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4401778435078635</v>
+        <v>0.4413048792033337</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02865493260682634</v>
+        <v>0.03024831177244883</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8092611685647835</v>
+        <v>0.810704364561122</v>
       </c>
       <c r="J16" t="n">
-        <v>0.815018096663622</v>
+        <v>0.8138730253477729</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6696245001715595</v>
+        <v>0.6702136941551101</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5847765502454479</v>
+        <v>0.5851060149132756</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8239664337557757</v>
+        <v>0.8255682848187462</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1461069991012891</v>
+        <v>0.1468335289314462</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4928417920543844</v>
+        <v>0.4919536505218504</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6796849393576251</v>
+        <v>0.6804427552543283</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.7987701287859842</v>
+        <v>0.7983720647296081</v>
       </c>
     </row>
     <row r="17">
@@ -1347,52 +1347,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1511740114427554</v>
+        <v>0.1491694754395926</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4206154737042943</v>
+        <v>0.4224573811872727</v>
       </c>
       <c r="D17" t="n">
-        <v>0.006131547132480769</v>
+        <v>0.005865482186483364</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5915290245380619</v>
+        <v>0.5924505987124155</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2374022960091234</v>
+        <v>0.2361890273894493</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3073798547678656</v>
+        <v>0.3060538957841619</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0003847820506757464</v>
+        <v>0.001406441020923477</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6392462182244774</v>
+        <v>0.6388414253312953</v>
       </c>
       <c r="J17" t="n">
-        <v>0.717535092750595</v>
+        <v>0.7185791217611988</v>
       </c>
       <c r="K17" t="n">
-        <v>0.632226329131013</v>
+        <v>0.6335664021321887</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3664098477858573</v>
+        <v>0.3668406675398739</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8107866556195006</v>
+        <v>0.8086467247171324</v>
       </c>
       <c r="N17" t="n">
-        <v>0.02110634611631959</v>
+        <v>0.02237079133040291</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1891051517065954</v>
+        <v>0.1873308107966259</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8331530635381221</v>
+        <v>0.8354124751706521</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.7857403602184859</v>
+        <v>0.7891330264727597</v>
       </c>
     </row>
     <row r="18">
@@ -1402,52 +1402,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.09585708701736326</v>
+        <v>0.09425871488731949</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8428069504628981</v>
+        <v>0.8438925968194001</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0002005810387004077</v>
+        <v>-6.075202889755437e-05</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4220143599202811</v>
+        <v>0.4202504963652168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1419516408857933</v>
+        <v>0.1458706796755928</v>
       </c>
       <c r="G18" t="n">
-        <v>0.159920937062443</v>
+        <v>0.1631161941434191</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01446473217975953</v>
+        <v>0.01299910999109119</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5300997983510817</v>
+        <v>0.5302588688166793</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5637774641981292</v>
+        <v>0.5649441185239549</v>
       </c>
       <c r="K18" t="n">
-        <v>0.486820595940708</v>
+        <v>0.4870385521125042</v>
       </c>
       <c r="L18" t="n">
-        <v>0.3648014436801721</v>
+        <v>0.3647826774806204</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6354639259663725</v>
+        <v>0.6376078064383177</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3385881471651526</v>
+        <v>0.3385396877000309</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3450674033531068</v>
+        <v>0.3453422767594735</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9394009033601753</v>
+        <v>0.9400797839835732</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5099704869877525</v>
+        <v>0.5113934215823004</v>
       </c>
     </row>
     <row r="19">
@@ -1457,52 +1457,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1468390543664329</v>
+        <v>0.1494379780316085</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7594401634085175</v>
+        <v>0.7591654319129472</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0174439392243368</v>
+        <v>0.01685113660987883</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5068626549445707</v>
+        <v>0.5047118873193541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05915514869519783</v>
+        <v>0.05832854543774366</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1234115600476263</v>
+        <v>0.1222082071041099</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0002218143079748734</v>
+        <v>-0.000552973758851798</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3700542737287266</v>
+        <v>0.3691085841519973</v>
       </c>
       <c r="J19" t="n">
-        <v>0.581920573172377</v>
+        <v>0.5840405048327534</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4985668975527855</v>
+        <v>0.4970767963140715</v>
       </c>
       <c r="L19" t="n">
-        <v>0.315428519748968</v>
+        <v>0.31695788631984</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6966195844913399</v>
+        <v>0.6969194927880543</v>
       </c>
       <c r="N19" t="n">
-        <v>0.05069168297008964</v>
+        <v>0.04984946270632434</v>
       </c>
       <c r="O19" t="n">
-        <v>0.07013447529900424</v>
+        <v>0.07176171415154294</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5834051260021736</v>
+        <v>0.5845011834541264</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5998757656874997</v>
+        <v>0.5989329615456345</v>
       </c>
     </row>
     <row r="20">
@@ -1512,52 +1512,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1214957433242936</v>
+        <v>0.1223353547067958</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1573760605668703</v>
+        <v>0.1563666337511804</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0009831203333245456</v>
+        <v>0.001183558486705375</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5494490634551548</v>
+        <v>0.5514949413984317</v>
       </c>
       <c r="F20" t="n">
-        <v>0.539253366820713</v>
+        <v>0.5416511771283833</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5260564305074128</v>
+        <v>0.5248679803624683</v>
       </c>
       <c r="H20" t="n">
-        <v>0.004144115890869501</v>
+        <v>0.004354241512647045</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6905462973552667</v>
+        <v>0.6886465876847876</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7050473341464198</v>
+        <v>0.7059520595139526</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7197073954720918</v>
+        <v>0.7190336677517605</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6496409219208897</v>
+        <v>0.6500194644955485</v>
       </c>
       <c r="M20" t="n">
-        <v>0.749612294447295</v>
+        <v>0.7517436791938121</v>
       </c>
       <c r="N20" t="n">
-        <v>0.00525210693059219</v>
+        <v>0.007518066435284892</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8261055237403</v>
+        <v>0.8266089616291599</v>
       </c>
       <c r="P20" t="n">
-        <v>0.363869038772937</v>
+        <v>0.3649858223884536</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.7957543838917801</v>
+        <v>0.7948280027244798</v>
       </c>
     </row>
     <row r="21">
@@ -1567,52 +1567,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1592862223278919</v>
+        <v>0.1588294957807712</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3744546633963591</v>
+        <v>0.3719142489370287</v>
       </c>
       <c r="D21" t="n">
-        <v>0.004128137876426421</v>
+        <v>0.005529037115968849</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7612121697542552</v>
+        <v>0.760591297512684</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4327057472484021</v>
+        <v>0.4322172644963095</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4630176410857878</v>
+        <v>0.4637320785464999</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03368285309273328</v>
+        <v>0.03543051143846025</v>
       </c>
       <c r="I21" t="n">
-        <v>0.788866192497471</v>
+        <v>0.7896119855326532</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8123558263549356</v>
+        <v>0.8125933962837185</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6879379039559115</v>
+        <v>0.687548992855136</v>
       </c>
       <c r="L21" t="n">
-        <v>0.511924273079578</v>
+        <v>0.5114612635091673</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8451797007185866</v>
+        <v>0.8440152914808275</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2398030929747684</v>
+        <v>0.2394721496741159</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8234702466957972</v>
+        <v>0.8230165467992824</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2277018311010067</v>
+        <v>0.2276750090197921</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.768141386367746</v>
+        <v>0.768336659988514</v>
       </c>
     </row>
     <row r="22">
@@ -1622,52 +1622,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2192689729499379</v>
+        <v>0.2186594123129504</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2268209035832907</v>
+        <v>0.2302435217730741</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01168527832007378</v>
+        <v>0.01248975085799808</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4553300541881496</v>
+        <v>0.4547727917547212</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2700962849979401</v>
+        <v>0.2704803769420275</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3354531829653002</v>
+        <v>0.3336994600169511</v>
       </c>
       <c r="H22" t="n">
-        <v>0.005990134850190927</v>
+        <v>0.007361613786211162</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4802902669970819</v>
+        <v>0.4797929761830694</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7520213229563713</v>
+        <v>0.7512901413565561</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6422408048126413</v>
+        <v>0.641461116554276</v>
       </c>
       <c r="L22" t="n">
-        <v>0.3707668603190195</v>
+        <v>0.3720799389705451</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7817100423166015</v>
+        <v>0.7822140675079845</v>
       </c>
       <c r="N22" t="n">
-        <v>0.07802400135983839</v>
+        <v>0.07644277722755287</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3491925278398841</v>
+        <v>0.3499772235682288</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5167252046124811</v>
+        <v>0.5182904228153046</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7400252265480863</v>
+        <v>0.7371898806792451</v>
       </c>
     </row>
     <row r="23">
@@ -1677,52 +1677,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2177079106815134</v>
+        <v>0.2184096755199154</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2781283046216951</v>
+        <v>0.2779613934085273</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02484656630121298</v>
+        <v>0.02608556271550888</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4699472050959974</v>
+        <v>0.4711966273711912</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4210370036431172</v>
+        <v>0.4210773962525183</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5696434260906124</v>
+        <v>0.56768806021427</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01216493248150689</v>
+        <v>0.01124842267621506</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6004049528903115</v>
+        <v>0.6009636733251883</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9212309418129824</v>
+        <v>0.9220564839085054</v>
       </c>
       <c r="K23" t="n">
-        <v>0.795939624265618</v>
+        <v>0.7964128562294803</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6517308799241475</v>
+        <v>0.6523130415466467</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9462876462034604</v>
+        <v>0.9437776786115164</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04989481870807311</v>
+        <v>0.04865540246177735</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4504491641434111</v>
+        <v>0.4504440142125645</v>
       </c>
       <c r="P23" t="n">
-        <v>0.5880074662392479</v>
+        <v>0.5876246914330869</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.895274727251779</v>
+        <v>0.8950081356099979</v>
       </c>
     </row>
     <row r="24">
@@ -1732,52 +1732,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2713138406100522</v>
+        <v>0.2691597029478291</v>
       </c>
       <c r="C24" t="n">
-        <v>0.09869646456016662</v>
+        <v>0.09889833939182931</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00228906008296254</v>
+        <v>0.002669825937139383</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4445181510370252</v>
+        <v>0.4459751285891402</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8136028570721926</v>
+        <v>0.8152644008951421</v>
       </c>
       <c r="G24" t="n">
-        <v>0.822137135828263</v>
+        <v>0.8222915572971796</v>
       </c>
       <c r="H24" t="n">
-        <v>0.001099895224341404</v>
+        <v>0.001203650493630433</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6706491655800668</v>
+        <v>0.6696529214398362</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9046244243849371</v>
+        <v>0.9052621598307797</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8397197192715599</v>
+        <v>0.8404029597200623</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6491426293053969</v>
+        <v>0.6492176291717896</v>
       </c>
       <c r="M24" t="n">
-        <v>0.930516988217794</v>
+        <v>0.9295870152336879</v>
       </c>
       <c r="N24" t="n">
-        <v>0.009033007730118893</v>
+        <v>0.01009501668145312</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5266098489497734</v>
+        <v>0.5267323032816463</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4838450900531603</v>
+        <v>0.4828329873266428</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.952798563012375</v>
+        <v>0.9536036900577346</v>
       </c>
     </row>
     <row r="25">
@@ -1787,52 +1787,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.2799294715604401</v>
+        <v>0.2793650430225497</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1447519896745872</v>
+        <v>0.144128853318015</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1559621038120342</v>
+        <v>0.156908680460395</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8830332794369181</v>
+        <v>0.8857280701857595</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5068912932689332</v>
+        <v>0.5090381193557219</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5403373344164463</v>
+        <v>0.5409117836172049</v>
       </c>
       <c r="H25" t="n">
-        <v>1.000623794778504</v>
+        <v>1.00022312099082</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7504758705581671</v>
+        <v>0.7492575979136731</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8630393501362198</v>
+        <v>0.8611376010140616</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6679430071199401</v>
+        <v>0.6691728257419484</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4831571145357748</v>
+        <v>0.4820454038704958</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8701535084823835</v>
+        <v>0.8684976353701457</v>
       </c>
       <c r="N25" t="n">
-        <v>0.6005801928845127</v>
+        <v>0.5993008975627342</v>
       </c>
       <c r="O25" t="n">
-        <v>0.723921791575604</v>
+        <v>0.7252759324135905</v>
       </c>
       <c r="P25" t="n">
-        <v>0.1644141279140493</v>
+        <v>0.1648218172936551</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.80597450130212</v>
+        <v>0.804543455243118</v>
       </c>
     </row>
     <row r="26">
@@ -1842,52 +1842,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07524233674153996</v>
+        <v>0.0740806265992851</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7473914332067765</v>
+        <v>0.7448679775986801</v>
       </c>
       <c r="D26" t="n">
-        <v>0.04686734840344759</v>
+        <v>0.04578355848345109</v>
       </c>
       <c r="E26" t="n">
-        <v>0.7383169973723743</v>
+        <v>0.7376625208044861</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3409075683984692</v>
+        <v>0.3419199148727852</v>
       </c>
       <c r="G26" t="n">
-        <v>0.456212569389721</v>
+        <v>0.4549043879444355</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.0002830558707745175</v>
+        <v>-0.0002818583086393826</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8498600857555315</v>
+        <v>0.8511723115909564</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8950048407497825</v>
+        <v>0.8949857867208337</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6634539538197951</v>
+        <v>0.6630383606746847</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4889535528110371</v>
+        <v>0.489062985043966</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7813599009293131</v>
+        <v>0.7810544678618934</v>
       </c>
       <c r="N26" t="n">
-        <v>0.9983036879341004</v>
+        <v>0.999349280748914</v>
       </c>
       <c r="O26" t="n">
-        <v>0.007630288916590329</v>
+        <v>0.00803269462766186</v>
       </c>
       <c r="P26" t="n">
-        <v>1.000474739817699</v>
+        <v>1.000416746964389</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.7567841544471317</v>
+        <v>0.7538961556636776</v>
       </c>
     </row>
     <row r="27">
@@ -1897,52 +1897,52 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1176273722461122</v>
+        <v>0.1190595763192144</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2289341015004967</v>
+        <v>0.2288579869974132</v>
       </c>
       <c r="D27" t="n">
-        <v>0.003708218764605218</v>
+        <v>0.00327711487665923</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9927827238023829</v>
+        <v>0.9933979389785793</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7195886254736318</v>
+        <v>0.720622350314731</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8270896300106072</v>
+        <v>0.8280538713050527</v>
       </c>
       <c r="H27" t="n">
-        <v>8.574213420643251e-05</v>
+        <v>0.0006896566829726409</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9998232449171069</v>
+        <v>1.000166281615518</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9821533137249405</v>
+        <v>0.9831441372936311</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8947112515694544</v>
+        <v>0.892524474797469</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6553446287465874</v>
+        <v>0.6557885041747895</v>
       </c>
       <c r="M27" t="n">
-        <v>0.8432827820542161</v>
+        <v>0.8426424916462169</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0003408337396861178</v>
+        <v>0.001198840069149301</v>
       </c>
       <c r="O27" t="n">
-        <v>0.3197699201530519</v>
+        <v>0.319844989751811</v>
       </c>
       <c r="P27" t="n">
-        <v>0.01130119086187066</v>
+        <v>0.009994661257276712</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.936392271554662</v>
+        <v>0.9340778031845983</v>
       </c>
     </row>
     <row r="28">
@@ -1952,52 +1952,52 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0945702983907722</v>
+        <v>0.09524215345319376</v>
       </c>
       <c r="C28" t="n">
-        <v>0.21849864950868</v>
+        <v>0.2168777224835267</v>
       </c>
       <c r="D28" t="n">
-        <v>0.004874183144699706</v>
+        <v>0.003160591884695605</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4519192977152581</v>
+        <v>0.4531189803211467</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5297584402350781</v>
+        <v>0.5309981844519212</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6340758302949244</v>
+        <v>0.6331781995401682</v>
       </c>
       <c r="H28" t="n">
-        <v>0.001941909765946382</v>
+        <v>0.002388966490280699</v>
       </c>
       <c r="I28" t="n">
-        <v>0.540149942774477</v>
+        <v>0.5399721436287782</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9021318829352962</v>
+        <v>0.8992356958643855</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7990901289074858</v>
+        <v>0.7989547070276095</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7721157061129622</v>
+        <v>0.7728586582617792</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9247527111237277</v>
+        <v>0.9246373851807402</v>
       </c>
       <c r="N28" t="n">
-        <v>0.01042631237142941</v>
+        <v>0.0113032784458357</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5850139045377243</v>
+        <v>0.5832487775670062</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4856430872443904</v>
+        <v>0.4857132563588966</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.9252113922995769</v>
+        <v>0.9247338159259151</v>
       </c>
     </row>
     <row r="29">
@@ -2007,52 +2007,52 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3127357133889614</v>
+        <v>0.3119687224197745</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3485248416594193</v>
+        <v>0.3483736652102999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.03468193092285649</v>
+        <v>0.03617517981012717</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5249446375955602</v>
+        <v>0.524562155104929</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2309770671188629</v>
+        <v>0.2317368755002609</v>
       </c>
       <c r="G29" t="n">
-        <v>0.3012261432957259</v>
+        <v>0.3014852965855696</v>
       </c>
       <c r="H29" t="n">
-        <v>0.002991109162042849</v>
+        <v>0.00236363613668731</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6792692611231178</v>
+        <v>0.6817859130524205</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7435980254524791</v>
+        <v>0.7412985263214414</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6419081813131897</v>
+        <v>0.6423980271667405</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4788054194979747</v>
+        <v>0.4790069690017988</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7488361180327953</v>
+        <v>0.7461235228997684</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2944520698355039</v>
+        <v>0.2959893612124884</v>
       </c>
       <c r="O29" t="n">
-        <v>0.2042886170213253</v>
+        <v>0.2043089364214814</v>
       </c>
       <c r="P29" t="n">
-        <v>0.9836901052719944</v>
+        <v>0.9837031146121505</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.7853516190410779</v>
+        <v>0.7875230891637235</v>
       </c>
     </row>
     <row r="30">
@@ -2062,52 +2062,52 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1564759043863491</v>
+        <v>0.1569466824061982</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3255318576108407</v>
+        <v>0.3247582427049936</v>
       </c>
       <c r="D30" t="n">
-        <v>0.05030284107974454</v>
+        <v>0.04968980407406311</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5282933800268137</v>
+        <v>0.5300403904841952</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6572252155085155</v>
+        <v>0.6548051653006732</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7872317205096168</v>
+        <v>0.7878133685853886</v>
       </c>
       <c r="H30" t="n">
-        <v>0.001419157049240964</v>
+        <v>0.001506029182994216</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8098785628886566</v>
+        <v>0.8099045656577869</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9583065997443202</v>
+        <v>0.9591099213387128</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8319273462835503</v>
+        <v>0.8318615660656306</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6047300610123747</v>
+        <v>0.6027958015366602</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9140957779893237</v>
+        <v>0.9140790214099499</v>
       </c>
       <c r="N30" t="n">
-        <v>0.009390560159035426</v>
+        <v>0.01193228156719878</v>
       </c>
       <c r="O30" t="n">
-        <v>0.9405041722452123</v>
+        <v>0.9387960962173829</v>
       </c>
       <c r="P30" t="n">
-        <v>0.208453088438182</v>
+        <v>0.2105528407676184</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8807964199941335</v>
+        <v>0.8798532219810299</v>
       </c>
     </row>
     <row r="31">
@@ -2117,52 +2117,52 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.3670985118895524</v>
+        <v>0.3646667069297908</v>
       </c>
       <c r="C31" t="n">
-        <v>0.1169870870188616</v>
+        <v>0.1159811289993756</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01932672318209498</v>
+        <v>0.01775732280210607</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4166598062327267</v>
+        <v>0.4173498564737735</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7711742934850599</v>
+        <v>0.7712194763168038</v>
       </c>
       <c r="G31" t="n">
-        <v>0.8388251563628289</v>
+        <v>0.8386863163206855</v>
       </c>
       <c r="H31" t="n">
-        <v>0.006788066949370946</v>
+        <v>0.006790174311398166</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8092436678342995</v>
+        <v>0.8104137148209976</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9468449755846229</v>
+        <v>0.9464394670540419</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8553309301261777</v>
+        <v>0.8536250565285178</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7286585752481985</v>
+        <v>0.7281346133946769</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9394467504693986</v>
+        <v>0.9389292356322805</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0057940481623403</v>
+        <v>0.006836721780592341</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5404904624588887</v>
+        <v>0.5430347733203684</v>
       </c>
       <c r="P31" t="n">
-        <v>0.6498810988450253</v>
+        <v>0.6478644888517869</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9596883059147717</v>
+        <v>0.9589206225790924</v>
       </c>
     </row>
     <row r="32">
@@ -2172,52 +2172,52 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.1935093329737778</v>
+        <v>0.1940513998808635</v>
       </c>
       <c r="C32" t="n">
-        <v>0.06733030555160488</v>
+        <v>0.06736013675725973</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00435359700720848</v>
+        <v>0.00336965611261343</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7725697937763933</v>
+        <v>0.7702450686292751</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9795610495055205</v>
+        <v>0.9798926664141228</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9994136421175148</v>
+        <v>0.9986792221961293</v>
       </c>
       <c r="H32" t="n">
-        <v>0.05056289850110299</v>
+        <v>0.05059643028979916</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8792719999646171</v>
+        <v>0.8800516029146236</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9894048036157569</v>
+        <v>0.9897794669455271</v>
       </c>
       <c r="K32" t="n">
-        <v>0.9397838214246278</v>
+        <v>0.9384880041340395</v>
       </c>
       <c r="L32" t="n">
-        <v>0.9357129782023915</v>
+        <v>0.9362461941781349</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9985005440291437</v>
+        <v>1.000436870965094</v>
       </c>
       <c r="N32" t="n">
-        <v>0.04859586527727187</v>
+        <v>0.04951750928639533</v>
       </c>
       <c r="O32" t="n">
-        <v>0.9985104176502952</v>
+        <v>1.002018621619869</v>
       </c>
       <c r="P32" t="n">
-        <v>0.09240249349388571</v>
+        <v>0.09298828300071259</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.9999151725915453</v>
+        <v>0.999168658946479</v>
       </c>
     </row>
     <row r="33">
@@ -2227,52 +2227,52 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2045822218876976</v>
+        <v>0.2021319399074059</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3258305867771465</v>
+        <v>0.3251390487876268</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02272580362264643</v>
+        <v>0.02198859090533927</v>
       </c>
       <c r="E33" t="n">
-        <v>0.403822079834153</v>
+        <v>0.4042395095273064</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3579793422338812</v>
+        <v>0.3569874859205109</v>
       </c>
       <c r="G33" t="n">
-        <v>0.468327033155399</v>
+        <v>0.4707362794707439</v>
       </c>
       <c r="H33" t="n">
-        <v>0.01959062851306418</v>
+        <v>0.01921083633178981</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5195580682490161</v>
+        <v>0.5205311739713193</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8144633933031956</v>
+        <v>0.8155643707763018</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6847910793449268</v>
+        <v>0.6858434548008803</v>
       </c>
       <c r="L33" t="n">
-        <v>0.489494443941648</v>
+        <v>0.4899775322906197</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8682419956291039</v>
+        <v>0.8701822369482559</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0709466726373208</v>
+        <v>0.07087032589970797</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5673445694935728</v>
+        <v>0.5661073881922839</v>
       </c>
       <c r="P33" t="n">
-        <v>0.53611816662027</v>
+        <v>0.5354128929926821</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.819606427210779</v>
+        <v>0.8193680788464029</v>
       </c>
     </row>
     <row r="34">
@@ -2282,52 +2282,52 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.04195365556984539</v>
+        <v>0.04104362315290524</v>
       </c>
       <c r="C34" t="n">
-        <v>0.5303669269888082</v>
+        <v>0.5293630620242921</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0153324105322725</v>
+        <v>0.01500813418989209</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7731015443977889</v>
+        <v>0.7707735096992933</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4330682934194127</v>
+        <v>0.4336324376876522</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5309572781864595</v>
+        <v>0.5284496514469411</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.0006537418451534916</v>
+        <v>0.0009119980565888032</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8697509277601764</v>
+        <v>0.8706132387791427</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9301128447191883</v>
+        <v>0.9297974704162909</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7615469141641558</v>
+        <v>0.7605716927111522</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6743235150631566</v>
+        <v>0.6736147697093441</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8080155071869491</v>
+        <v>0.8080471686450894</v>
       </c>
       <c r="N34" t="n">
-        <v>0.6499290795954482</v>
+        <v>0.6503078940744083</v>
       </c>
       <c r="O34" t="n">
-        <v>0.06357173374866638</v>
+        <v>0.06747849743601746</v>
       </c>
       <c r="P34" t="n">
-        <v>0.0663892421564535</v>
+        <v>0.06638041969784787</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8459978709865923</v>
+        <v>0.8480570919983049</v>
       </c>
     </row>
     <row r="35">
@@ -2337,52 +2337,52 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.3453944062553219</v>
+        <v>0.3489814498864909</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1192885196258664</v>
+        <v>0.1186239448774926</v>
       </c>
       <c r="D35" t="n">
-        <v>0.02581803741401282</v>
+        <v>0.02723357031393641</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4696630051877906</v>
+        <v>0.4685500073454048</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8187406668578601</v>
+        <v>0.8186379969898503</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9000405885432861</v>
+        <v>0.901460484681429</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0016363337014079</v>
+        <v>0.0009221176130367407</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8412870577681932</v>
+        <v>0.8393458587618308</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9767603761763312</v>
+        <v>0.9750491695543985</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9001284816780296</v>
+        <v>0.9003497226364432</v>
       </c>
       <c r="L35" t="n">
-        <v>1.000393695334439</v>
+        <v>1.000484878243362</v>
       </c>
       <c r="M35" t="n">
-        <v>0.944038571318159</v>
+        <v>0.9447378598959426</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02155299660544616</v>
+        <v>0.02086712970304586</v>
       </c>
       <c r="O35" t="n">
-        <v>0.1928955776819141</v>
+        <v>0.1916721199577671</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8874497375407283</v>
+        <v>0.8865312338616193</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.9993311226434557</v>
+        <v>0.9977082976505639</v>
       </c>
     </row>
     <row r="36">
@@ -2392,52 +2392,52 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.001012817872851</v>
+        <v>0.9992903022871965</v>
       </c>
       <c r="C36" t="n">
-        <v>0.09300374803541174</v>
+        <v>0.09272324908577005</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3823186278411626</v>
+        <v>0.3799869612272119</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5884200115801779</v>
+        <v>0.5872218561822606</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8035668574354645</v>
+        <v>0.8017905125420137</v>
       </c>
       <c r="G36" t="n">
-        <v>0.8245992102761333</v>
+        <v>0.8247462574443155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.263538174861207</v>
+        <v>0.2625990515137647</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8312743106982607</v>
+        <v>0.8300106462353111</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9686359993480977</v>
+        <v>0.967660127109535</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8734918331515678</v>
+        <v>0.8734796023985827</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6570785674545206</v>
+        <v>0.6585004091192362</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8773798076232414</v>
+        <v>0.8731728175209541</v>
       </c>
       <c r="N36" t="n">
-        <v>0.02797727428100417</v>
+        <v>0.02836698444357469</v>
       </c>
       <c r="O36" t="n">
-        <v>0.494059759559418</v>
+        <v>0.495636931502191</v>
       </c>
       <c r="P36" t="n">
-        <v>0.5499160928189085</v>
+        <v>0.5505922366557421</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.9214456973905736</v>
+        <v>0.92005602342193</v>
       </c>
     </row>
   </sheetData>
